--- a/timesheet_template.xlsx
+++ b/timesheet_template.xlsx
@@ -15,10 +15,6 @@
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="Category_of_staff">#REF!</definedName>
-    <definedName name="countryW">#REF!</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
